--- a/output/pdf_financials_xlsx/ZFR.xlsx
+++ b/output/pdf_financials_xlsx/ZFR.xlsx
@@ -5510,43 +5510,43 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.393908</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.423268</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.556729</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.600853</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.022082</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.152476</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.384046</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.627802</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.899066</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.209357</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.341073</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.555414</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.716079</v>
       </c>
     </row>
     <row r="93">
@@ -8748,7 +8748,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10214,7 +10218,11 @@
           <t>Share-based payments reserve 393,908</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZFR.xlsx
+++ b/output/pdf_financials_xlsx/ZFR.xlsx
@@ -628,30 +628,20 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>0</v>
@@ -665,15 +655,11 @@
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,32 +748,22 @@
         <v>0.05651</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.107547</v>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11863</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.12513</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.050803</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.048716</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.251311</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.400913</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.351211</v>
@@ -801,15 +777,11 @@
       <c r="M7" s="3" t="n">
         <v>0.261563</v>
       </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N7" s="3" t="n">
+        <v>0.397208</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0.38216</v>
       </c>
     </row>
     <row r="8">
@@ -827,30 +799,20 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0</v>
@@ -864,15 +826,11 @@
       <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -890,30 +848,20 @@
       <c r="D9" s="3" t="n">
         <v>0.016301</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0.014426</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.015889</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.010503</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.019566</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.014171</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.009069000000000001</v>
@@ -927,15 +875,11 @@
       <c r="M9" s="3" t="n">
         <v>0.016948</v>
       </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" s="3" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0.015214</v>
       </c>
     </row>
     <row r="10">
@@ -951,32 +895,22 @@
         <v>0.569086</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.123848</v>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.134931</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.139556</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.066692</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.059219</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.270877</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.415084</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.36028</v>
@@ -990,15 +924,11 @@
       <c r="M10" s="3" t="n">
         <v>0.278511</v>
       </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N10" s="3" t="n">
+        <v>0.410248</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.397374</v>
       </c>
     </row>
     <row r="11">
@@ -1018,10 +948,8 @@
       <c r="D11" s="3" t="n">
         <v>-0.466955</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-0.335652</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1089,30 +1017,20 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1126,15 +1044,11 @@
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1152,30 +1066,20 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>-0</v>
@@ -1189,15 +1093,11 @@
       <c r="M13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1215,30 +1115,20 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>0</v>
@@ -1252,15 +1142,11 @@
       <c r="M14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1278,30 +1164,20 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-0.01739</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.012247</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.013303</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>-0.003798</v>
@@ -1315,15 +1191,11 @@
       <c r="M15" s="3" t="n">
         <v>-0.005961</v>
       </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N15" s="3" t="n">
+        <v>-0.021115</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0.004413</v>
       </c>
     </row>
     <row r="16">
@@ -1341,30 +1213,20 @@
       <c r="D16" s="3" t="n">
         <v>-0.701449</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-0.335652</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.178341</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-0.284432</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-0.34657</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.404331</v>
@@ -1378,15 +1240,11 @@
       <c r="M16" s="3" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" s="3" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="17">
@@ -1404,30 +1262,20 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1441,15 +1289,11 @@
       <c r="M17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1621,30 +1465,20 @@
       <c r="D20" s="3" t="n">
         <v>-0.701449</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-0.335652</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.178341</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-0.284432</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-0.34657</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.404331</v>
@@ -1658,15 +1492,11 @@
       <c r="M20" s="3" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" s="3" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="21">
@@ -1684,30 +1514,20 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1721,15 +1541,11 @@
       <c r="M21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1747,30 +1563,20 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -1784,15 +1590,11 @@
       <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1822,10 +1624,8 @@
       <c r="H23" s="3" t="n">
         <v>-0.34657</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.404331</v>
@@ -1839,15 +1639,11 @@
       <c r="M23" s="3" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" s="3" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="24">
@@ -1865,30 +1661,20 @@
       <c r="D24" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>-0.014</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>-0.008999999999999999</v>
@@ -1900,17 +1686,13 @@
         <v>-0.01</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-0.029</v>
       </c>
     </row>
     <row r="25">
@@ -1928,30 +1710,20 @@
       <c r="D25" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>-0.014</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>-0.008999999999999999</v>
@@ -1963,17 +1735,13 @@
         <v>-0.01</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>-0.029</v>
       </c>
     </row>
     <row r="26">
@@ -1993,30 +1761,24 @@
       <c r="D26" s="3" t="n">
         <v>14.02898</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>18.647333</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="3" t="n">
+        <v>25.857455</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="3" t="n">
+        <v>36.809857</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2036,15 +1798,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N26" s="3" t="n">
+        <v>70.074636</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>71.733448</v>
       </c>
     </row>
     <row r="27">
@@ -2062,30 +1820,20 @@
       <c r="D27" s="3" t="n">
         <v>-0.701449</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-0.335652</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.178341</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.284432</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-0.34657</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.404331</v>
@@ -2099,15 +1847,11 @@
       <c r="M27" s="3" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" s="3" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="28">
@@ -2125,30 +1869,20 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -2162,15 +1896,11 @@
       <c r="M28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2188,30 +1918,20 @@
       <c r="D29" s="3" t="n">
         <v>-0.701449</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-0.335652</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.178341</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-0.284432</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-0.34657</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.404331</v>
@@ -2225,15 +1945,11 @@
       <c r="M29" s="3" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N29" s="3" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="30">
@@ -2328,30 +2044,20 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -2365,15 +2071,11 @@
       <c r="M31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4171,43 +3873,43 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.077671</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.041142</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03749</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.025034</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.021554</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.025564</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.024229</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.021644</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.021575</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.026092</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.021965</v>
       </c>
     </row>
     <row r="68">
@@ -5856,10 +5558,8 @@
       <c r="H99" s="3" t="n">
         <v>-0.34657</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-0.404331</v>
@@ -5873,15 +5573,11 @@
       <c r="M99" s="3" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="100">
@@ -5911,10 +5607,8 @@
       <c r="H100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
@@ -5928,15 +5622,11 @@
       <c r="M100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5966,10 +5656,8 @@
       <c r="H101" s="3" t="n">
         <v>-0.012967</v>
       </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="3" t="n">
+        <v>-0.019771</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0.020311</v>
@@ -5983,15 +5671,11 @@
       <c r="M101" s="3" t="n">
         <v>-0.018831</v>
       </c>
-      <c r="N101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N101" s="3" t="n">
+        <v>0.025932</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>-0.004949</v>
       </c>
     </row>
     <row r="102">
@@ -6021,10 +5705,8 @@
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
         <v>0</v>
@@ -6038,15 +5720,11 @@
       <c r="M102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -6076,10 +5754,8 @@
       <c r="H103" s="3" t="n">
         <v>-0.055266</v>
       </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="3" t="n">
+        <v>-0.052614</v>
       </c>
       <c r="J103" s="3" t="n">
         <v>0.000796</v>
@@ -6093,15 +5769,11 @@
       <c r="M103" s="3" t="n">
         <v>0.010621</v>
       </c>
-      <c r="N103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N103" s="3" t="n">
+        <v>-0.011347</v>
+      </c>
+      <c r="O103" s="3" t="n">
+        <v>0.005361</v>
       </c>
     </row>
     <row r="104">
@@ -6131,10 +5803,8 @@
       <c r="H104" s="3" t="n">
         <v>0.099314</v>
       </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="3" t="n">
+        <v>-0.037526</v>
       </c>
       <c r="J104" s="3" t="n">
         <v>-0.043358</v>
@@ -6148,15 +5818,11 @@
       <c r="M104" s="3" t="n">
         <v>0.049895</v>
       </c>
-      <c r="N104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N104" s="3" t="n">
+        <v>-0.040614</v>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>0.01129</v>
       </c>
     </row>
     <row r="105">
@@ -6186,10 +5852,8 @@
       <c r="H105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
         <v>0</v>
@@ -6203,15 +5867,11 @@
       <c r="M105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -6241,10 +5901,8 @@
       <c r="H106" s="3" t="n">
         <v>0.031081</v>
       </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="3" t="n">
+        <v>-0.109911</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>-0.022251</v>
@@ -6258,15 +5916,11 @@
       <c r="M106" s="3" t="n">
         <v>0.041685</v>
       </c>
-      <c r="N106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N106" s="3" t="n">
+        <v>-0.026029</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>0.011702</v>
       </c>
     </row>
     <row r="107">
@@ -6296,10 +5950,8 @@
       <c r="H107" s="3" t="n">
         <v>0.02888</v>
       </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="3" t="n">
+        <v>0.043725</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>0.00175</v>
@@ -6313,15 +5965,11 @@
       <c r="M107" s="3" t="n">
         <v>0.272796</v>
       </c>
-      <c r="N107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N107" s="3" t="n">
+        <v>0.178683</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>0.093498</v>
       </c>
     </row>
     <row r="108">
@@ -6351,10 +5999,8 @@
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
@@ -6368,15 +6014,11 @@
       <c r="M108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6406,10 +6048,8 @@
       <c r="H109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
         <v>0</v>
@@ -6423,15 +6063,11 @@
       <c r="M109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6461,10 +6097,8 @@
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -6478,15 +6112,11 @@
       <c r="M110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6516,10 +6146,8 @@
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -6533,15 +6161,11 @@
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6571,10 +6195,8 @@
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -6588,15 +6210,11 @@
       <c r="M112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6626,10 +6244,8 @@
       <c r="H113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
         <v>0</v>
@@ -6643,15 +6259,11 @@
       <c r="M113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6681,10 +6293,8 @@
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -6698,15 +6308,11 @@
       <c r="M114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -6736,10 +6342,8 @@
       <c r="H115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -6753,15 +6357,11 @@
       <c r="M115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6791,10 +6391,8 @@
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -6808,15 +6406,11 @@
       <c r="M116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6846,10 +6440,8 @@
       <c r="H117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
         <v>0</v>
@@ -6863,15 +6455,11 @@
       <c r="M117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6899,12 +6487,10 @@
         <v>0.008156</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.941902</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>-0.753403</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>-1.032073</v>
@@ -6918,15 +6504,11 @@
       <c r="M118" s="3" t="n">
         <v>-0.43213</v>
       </c>
-      <c r="N118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N118" s="3" t="n">
+        <v>-0.032001</v>
+      </c>
+      <c r="O118" s="3" t="n">
+        <v>1.3504</v>
       </c>
     </row>
     <row r="119">
@@ -6956,10 +6538,8 @@
       <c r="H119" s="3" t="n">
         <v>-1.000902</v>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>-0.753403</v>
       </c>
       <c r="J119" s="3" t="n">
         <v>-1.032073</v>
@@ -6973,15 +6553,11 @@
       <c r="M119" s="3" t="n">
         <v>-0.43213</v>
       </c>
-      <c r="N119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N119" s="3" t="n">
+        <v>-0.113269</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>-0.157218</v>
       </c>
     </row>
     <row r="120">
@@ -7011,10 +6587,8 @@
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
@@ -7028,15 +6602,11 @@
       <c r="M120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -7066,10 +6636,8 @@
       <c r="H121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
@@ -7083,15 +6651,11 @@
       <c r="M121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7121,10 +6685,8 @@
       <c r="H122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
         <v>0</v>
@@ -7138,15 +6700,11 @@
       <c r="M122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7176,10 +6734,8 @@
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
         <v>0</v>
@@ -7193,15 +6749,11 @@
       <c r="M123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7231,10 +6783,8 @@
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -7248,15 +6798,11 @@
       <c r="M124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -7286,10 +6832,8 @@
       <c r="H125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -7303,15 +6847,11 @@
       <c r="M125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7341,10 +6881,8 @@
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -7358,15 +6896,11 @@
       <c r="M126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7473,10 +7007,8 @@
       <c r="H128" s="3" t="n">
         <v>0.201286</v>
       </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="3" t="n">
+        <v>1.119031</v>
       </c>
       <c r="J128" s="3" t="n">
         <v>1.543985</v>
@@ -7490,15 +7022,11 @@
       <c r="M128" s="3" t="n">
         <v>0.04835</v>
       </c>
-      <c r="N128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N128" s="3" t="n">
+        <v>0.303793</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>0.338517</v>
       </c>
     </row>
     <row r="129">
@@ -7528,10 +7056,8 @@
       <c r="H129" s="3" t="n">
         <v>0.201286</v>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>1.119031</v>
       </c>
       <c r="J129" s="3" t="n">
         <v>1.543985</v>
@@ -7545,15 +7071,11 @@
       <c r="M129" s="3" t="n">
         <v>0.04835</v>
       </c>
-      <c r="N129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N129" s="3" t="n">
+        <v>0.303793</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>0.338517</v>
       </c>
     </row>
     <row r="130">
@@ -7583,10 +7105,8 @@
       <c r="H130" s="3" t="n">
         <v>1.316332</v>
       </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="3" t="n">
+        <v>0.230107</v>
       </c>
       <c r="J130" s="3" t="n">
         <v>0.014211</v>
@@ -7600,15 +7120,11 @@
       <c r="M130" s="3" t="n">
         <v>1.421552</v>
       </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N130" s="3" t="n">
+        <v>0.712863</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>0.402953</v>
       </c>
     </row>
     <row r="131">
@@ -7638,10 +7154,8 @@
       <c r="H131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
         <v>0</v>
@@ -7655,15 +7169,11 @@
       <c r="M131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7693,10 +7203,8 @@
       <c r="H132" s="3" t="n">
         <v>-1.086225</v>
       </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="3" t="n">
+        <v>-0.215896</v>
       </c>
       <c r="J132" s="3" t="n">
         <v>0.08708</v>
@@ -7710,15 +7218,11 @@
       <c r="M132" s="3" t="n">
         <v>-0.708689</v>
       </c>
-      <c r="N132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N132" s="3" t="n">
+        <v>-0.30991</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>-0.286153</v>
       </c>
     </row>
     <row r="133">
@@ -7748,10 +7252,8 @@
       <c r="H133" s="3" t="n">
         <v>0.230107</v>
       </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="3" t="n">
+        <v>0.014211</v>
       </c>
       <c r="J133" s="3" t="n">
         <v>0.101291</v>
@@ -7765,15 +7267,11 @@
       <c r="M133" s="3" t="n">
         <v>0.712863</v>
       </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N133" s="3" t="n">
+        <v>0.402953</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>0.1168</v>
       </c>
     </row>
     <row r="134">
@@ -7803,10 +7301,8 @@
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -7820,15 +7316,11 @@
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7858,10 +7350,8 @@
       <c r="H135" s="3" t="n">
         <v>-0.286609</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>-0.581524</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.424832</v>
@@ -7875,15 +7365,11 @@
       <c r="M135" s="3" t="n">
         <v>-0.324909</v>
       </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N135" s="3" t="n">
+        <v>-0.500434</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>-0.467452</v>
       </c>
     </row>
   </sheetData>
@@ -7897,7 +7383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:R123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10422,10 +9908,8 @@
       <c r="K32" s="5" t="n">
         <v>-0.34657</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L32" s="5" t="n">
+        <v>-0.515338</v>
       </c>
       <c r="M32" s="5" t="n">
         <v>-0.404331</v>
@@ -10439,15 +9923,11 @@
       <c r="P32" s="5" t="n">
         <v>-0.625417</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q32" s="5" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="33">
@@ -10498,10 +9978,8 @@
       <c r="K33" s="5" t="n">
         <v>0.02888</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L33" s="5" t="n">
+        <v>0.043725</v>
       </c>
       <c r="M33" s="5" t="n">
         <v>0.00175</v>
@@ -10515,15 +9993,11 @@
       <c r="P33" s="5" t="n">
         <v>0.272796</v>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q33" s="5" t="n">
+        <v>0.178683</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0.093498</v>
       </c>
     </row>
     <row r="34">
@@ -10534,66 +10008,84 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not requiring an outlay of cash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Impairment on exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>-0.008498</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>-0.010258</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>-0.00667</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0.017596</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0.006828</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>-0.004943</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>-0.012967</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M34" s="5" t="n">
-        <v>0.020311</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0.01323</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>-0.01151</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>-0.018831</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0.08126800000000001</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>1.507618</v>
       </c>
     </row>
     <row r="35">
@@ -10609,61 +10101,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.011089</v>
+        <v>-0.008498</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.011089</v>
+        <v>-0.010258</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.009091999999999999</v>
+        <v>-0.00667</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-0.031745</v>
+        <v>0.017596</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.008862</v>
+        <v>0.006828</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.028444</v>
+        <v>-0.004943</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.055266</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.012967</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>-0.019771</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.000796</v>
+        <v>0.020311</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>-0.022439</v>
+        <v>0.01323</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.014398</v>
+        <v>-0.01151</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.010621</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.018831</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0.025932</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>-0.004949</v>
       </c>
     </row>
     <row r="36">
@@ -10679,73 +10165,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reclamation bonds</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>-0.011089</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.011089</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.009091999999999999</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>-0.031745</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>-0.008862</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0.028444</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>-0.055266</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-0.052614</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0.000796</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.022439</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>-0.016961</v>
+        <v>0.014398</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>-0.013973</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010621</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>-0.011347</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0.005361</v>
       </c>
     </row>
     <row r="37">
@@ -10761,58 +10229,66 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Reclamation bonds</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>0.003947</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.062359</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>-0.07804999999999999</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>0.032331</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>0.099314</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="5" t="n">
-        <v>-0.043358</v>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N37" s="5" t="n">
-        <v>-0.037781</v>
+        <v>0.005</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>-0.009383000000000001</v>
+        <v>-0.016961</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.049895</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013973</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>0.036465</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -10833,61 +10309,57 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash Used in Operating Activities</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>-0.029645</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.2434</v>
+        <v>0.003947</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.393757</v>
+        <v>0.062359</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>-0.378921</v>
+        <v>-0.07804999999999999</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>-0.148044</v>
+        <v>0.032331</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.129411</v>
+        <v>0.0114</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.286609</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.099314</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>-0.037526</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>-0.424832</v>
+        <v>-0.043358</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>-0.437689</v>
+        <v>-0.037781</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>-0.447841</v>
+        <v>-0.009383000000000001</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>-0.324909</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.049895</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>-0.040614</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0.01129</v>
       </c>
     </row>
     <row r="39">
@@ -10898,74 +10370,60 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Expenditures on exploration and evaluation assets</t>
+          <t>Cash Used in Operating Activities</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>-0.029645</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.2434</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.393757</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>-0.430566</v>
+        <v>-0.378921</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>-0.102333</v>
+        <v>-0.148044</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.181539</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.129411</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.286609</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>-0.581524</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-1.032073</v>
+        <v>-0.424832</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>-0.506208</v>
+        <v>-0.437689</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>-1.456903</v>
+        <v>-0.447841</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>-0.43213</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.324909</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>-0.500434</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>-0.467452</v>
       </c>
     </row>
     <row r="40">
@@ -10981,12 +10439,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash Used for Investing Activities</t>
+          <t>Expenditures on exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10994,8 +10452,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>-0.08993900000000001</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -11014,10 +10474,8 @@
       <c r="K40" s="5" t="n">
         <v>-1.000902</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L40" s="5" t="n">
+        <v>-0.753403</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>-1.032073</v>
@@ -11031,15 +10489,11 @@
       <c r="P40" s="5" t="n">
         <v>-0.43213</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q40" s="5" t="n">
+        <v>-0.153871</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>-0.157218</v>
       </c>
     </row>
     <row r="41">
@@ -11050,61 +10504,81 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Issue of common shares net of share issue costs</t>
+          <t>Proceeds from sale of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0.449286</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>0.60834</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.273775</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.646669</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0.252908</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>1.524975</v>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>0.201286</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M41" s="5" t="n">
-        <v>1.543985</v>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v>0.941236</v>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v>3.227666</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0.04835</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0.040602</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -11120,68 +10594,64 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash Provided by Financing Activities</t>
+          <t>Cash Used for Investing Activities</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.449286</v>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.60834</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.273775</v>
+        <v>-0.08993900000000001</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.668169</v>
+        <v>-0.430566</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.252908</v>
+        <v>-0.102333</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1.534975</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.181539</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>-1.000902</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.753403</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>1.543985</v>
+        <v>-1.032073</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.941236</v>
+        <v>-0.506208</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>3.227666</v>
+        <v>-1.456903</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.04835</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.43213</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>-0.113269</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>-0.157218</v>
       </c>
     </row>
     <row r="43">
@@ -11197,65 +10667,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issue of common shares net of share issue costs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.449286</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.60834</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.273775</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>-0.141318</v>
+        <v>0.646669</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>0.002531</v>
+        <v>0.252908</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1.224025</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.524975</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.201286</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>1.119031</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.08708</v>
+        <v>1.543985</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>-0.002661</v>
+        <v>0.941236</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>1.322922</v>
+        <v>3.227666</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>-0.708689</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.04835</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>0.303793</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0.338517</v>
       </c>
     </row>
     <row r="44">
@@ -11271,69 +10731,55 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, Beginning of Year</t>
+          <t>Cash Provided by Financing Activities</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.449286</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.60834</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.273775</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.231094</v>
+        <v>0.668169</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.08977599999999999</v>
+        <v>0.252908</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.092307</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.534975</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.201286</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>1.119031</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.014211</v>
+        <v>1.543985</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.101291</v>
+        <v>0.941236</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.09863</v>
+        <v>3.227666</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>1.421552</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.04835</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0.303793</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0.338517</v>
       </c>
     </row>
     <row r="45">
@@ -11349,14 +10795,10 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, End of Year $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -11373,45 +10815,37 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.08977599999999999</v>
+        <v>-0.141318</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.092307</v>
+        <v>0.002531</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>1.316332</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.224025</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>-1.086225</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.215896</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.101291</v>
+        <v>0.08708</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.09863</v>
+        <v>-0.002661</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>1.421552</v>
+        <v>1.322922</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.712863</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.708689</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>-0.30991</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>-0.286153</v>
       </c>
     </row>
     <row r="46">
@@ -11422,15 +10856,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Non-cash financing and investing activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash paid for interest $</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Cash and Cash Equivalents, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11446,60 +10884,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H46" s="5" t="n">
+        <v>0.231094</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0.08977599999999999</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0.092307</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>1.316332</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0.230107</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0.014211</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0.101291</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0.09863</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>1.421552</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0.712863</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0.402953</v>
       </c>
     </row>
     <row r="47">
@@ -11510,15 +10926,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Non-cash financing and investing activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash paid for income taxes $</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Cash and Cash Equivalents, End of Year $</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -11534,60 +10954,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H47" s="5" t="n">
+        <v>0.08977599999999999</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.092307</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>1.316332</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.230107</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.014211</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.101291</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.09863</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>1.421552</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.712863</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>0.402953</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>0.1168</v>
       </c>
     </row>
     <row r="48">
@@ -11603,7 +11001,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Value of brokers warrants issued $</t>
+          <t>Cash paid for interest $</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -11647,14 +11045,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M48" s="5" t="n">
-        <v>0.027239</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0.006041</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0.034116</v>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -11685,7 +11089,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Reclamation accrual $</t>
+          <t>Cash paid for income taxes $</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -11734,14 +11138,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N49" s="5" t="n">
-        <v>0.021169</v>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v>0.000781</v>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v>0.015055</v>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -11762,19 +11172,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Exercise of options                                                               10,000</t>
+          <t>Non-cash financing and investing activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cash Provided by Financing Activities</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Value of brokers warrants issued $</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -11800,46 +11206,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>1.534975</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>0.201286</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0.00305</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0.027239</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0.006041</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0.034116</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q50" s="5" t="n">
+        <v>0.001481</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0.003225</v>
       </c>
     </row>
     <row r="51">
@@ -11850,12 +11248,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Exercise of options                                                               10,000</t>
+          <t>Non-cash financing and investing activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Reclamation accrual $</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -11884,41 +11282,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J51" s="5" t="n">
-        <v>1.224025</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>-1.086225</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.032317</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N51" s="5" t="n">
+        <v>0.021169</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.000781</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>0.015055</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>0.061442</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -11934,17 +11326,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Exercise of options                                                               10,000</t>
+          <t>Items not requiring an outlay of cash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, Beginning of Year</t>
+          <t>Loss on disposition of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11972,11 +11364,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J52" s="5" t="n">
-        <v>0.092307</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>1.316332</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -12003,10 +11399,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q52" s="5" t="n">
+        <v>0.08126800000000001</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -12022,17 +11416,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Exercise of options                                                               10,000</t>
+          <t>Value of share based payments charged to exploration</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, End of Year $</t>
+          <t>Value of share based payments charged to exploration and evaluation assets $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -12055,16 +11449,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="5" t="n">
+        <v>0.018344</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1.316332</v>
+        <v>0.008156</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.230107</v>
+        <v>0.059</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -12115,14 +11507,10 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Value of share based payments charged to exploration and evaluation assets $</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Value of brokers warrants issued $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -12143,19 +11531,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n">
-        <v>0.018344</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0.008156</v>
+        <v>0.027</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002703</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.00305</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -12201,7 +11589,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Value of brokers warrants issued $</t>
+          <t>Reclamation accrual $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -12230,16 +11618,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J55" s="5" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>0.002703</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.032317</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -12280,15 +11670,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Exercise of options                                                               10,000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Exercise of options</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Cash Provided by Financing Activities</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -12315,12 +11709,10 @@
         </is>
       </c>
       <c r="J56" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.534975</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.201286</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -12366,12 +11758,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Exercise of options                                                               10,000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Exercise of warrants</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -12390,23 +11782,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n">
-        <v>0.0215</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J57" s="5" t="n">
+        <v>1.224025</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>-1.086225</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -12452,15 +11842,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Items not requiring an outlay of cash</t>
+          <t>Exercise of options                                                               10,000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Impairment of mineral property</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Cash and Cash Equivalents, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12471,8 +11865,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>0.234494</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -12484,15 +11880,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J58" s="5" t="n">
+        <v>0.092307</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>1.316332</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -12538,17 +11930,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenditures on exploration and evaluation</t>
+          <t>Exercise of options                                                               10,000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Expenditures on exploration and evaluation assets</t>
+          <t>Cash and Cash Equivalents, End of Year $</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -12556,29 +11948,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>-0.08993900000000001</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.343566</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>-0.430566</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J59" s="5" t="n">
+        <v>1.316332</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.230107</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -12624,42 +12018,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenditures on exploration and evaluation</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash Used for Investing Activities</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Exercise of options</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F60" s="5" t="n">
-        <v>-0.08993900000000001</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.343566</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>-0.430566</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J60" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -12710,19 +12104,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Exercise of warrants                                           21,500</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cash Provided by Financing Activities</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -12733,11 +12123,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>0.273775</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.668169</v>
+        <v>0.0215</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -12798,12 +12190,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Exercise of warrants                                           21,500</t>
+          <t>Items not requiring an outlay of cash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Impairment of mineral property</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -12818,10 +12210,12 @@
         </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.463548</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>-0.141318</v>
+        <v>0.234494</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -12882,17 +12276,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Exercise of warrants                                           21,500</t>
+          <t>Expenditures on exploration and evaluation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, Beginning of Year</t>
+          <t>Expenditures on exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -12900,16 +12294,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" s="5" t="n">
+        <v>-0.08993900000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.694642</v>
+        <v>-0.343566</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.231094</v>
+        <v>-0.430566</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -12970,17 +12362,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Exercise of warrants                                           21,500</t>
+          <t>Expenditures on exploration and evaluation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, End of Year $</t>
+          <t>Cash Used for Investing Activities</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -12988,16 +12380,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="5" t="n">
+        <v>-0.08993900000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.231094</v>
+        <v>-0.343566</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.08977599999999999</v>
+        <v>-0.430566</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -13058,30 +12448,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Non-cash financing and investing activities</t>
+          <t>Exercise of warrants                                           21,500</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shares issued for interest in mining property</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Cash Provided by Financing Activities</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>0.0462</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.01672</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.273775</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.668169</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -13142,34 +12536,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Exercise of warrants                                           21,500</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Share based payments</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>0.320908</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.026601</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.463548</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>-0.141318</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -13230,15 +12620,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Exercise of warrants                                           21,500</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Impairment of mineral property</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Cash and Cash Equivalents, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -13250,12 +12644,10 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.234494</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.694642</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.231094</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -13316,30 +12708,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Net Change in Cash and Cash Equivalents for</t>
+          <t>Exercise of warrants                                           21,500</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net Change in Cash and Cash Equivalents for the year</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Cash and Cash Equivalents, End of Year $</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>0.275001</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.463548</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.231094</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.08977599999999999</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -13400,29 +12796,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Net Change in Cash and Cash Equivalents for</t>
+          <t>Non-cash financing and investing activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, Beginning of year</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Shares issued for interest in mining property</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.419641</v>
+        <v>0.0462</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.694642</v>
+        <v>0.01672</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -13488,17 +12880,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Net Change in Cash and Cash Equivalents for</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, End of year $</t>
+          <t>Share based payments</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -13507,10 +12899,10 @@
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.694642</v>
+        <v>0.320908</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.231094</v>
+        <v>0.026601</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -13576,25 +12968,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued</t>
+          <t>Impairment of mineral property</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.040198</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>0.003947</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.234494</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -13660,12 +13054,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Net Change in Cash and Cash Equivalents for</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Acquisition of mineral assets</t>
+          <t>Net Change in Cash and Cash Equivalents for the year</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -13675,12 +13069,10 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.08993900000000001</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.275001</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.463548</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -13751,20 +13143,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net Change in Cash and Cash Equivalents for the Period</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
+          <t>Cash and Cash Equivalents, Beginning of year</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>0.419641</v>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>0.275001</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G73" s="5" t="n">
+        <v>0.694642</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -13835,12 +13231,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, Beginning of</t>
+          <t>Cash and Cash Equivalents, End of year $</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -13849,12 +13245,10 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.419641</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.694642</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.231094</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -13920,24 +13314,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Net Change in Cash and Cash Equivalents for</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, End of Period $</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Accounts payable and accrued</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>0.419641</v>
+        <v>0.040198</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.694642</v>
+        <v>0.003947</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -14008,12 +13398,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Non-cash financing and investing activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Shares issued for interest in mining property $</t>
+          <t>Acquisition of mineral assets</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -14023,7 +13413,7 @@
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.0462</v>
+        <v>-0.08993900000000001</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -14089,33 +13479,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Net Change in Cash and Cash Equivalents for</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Filing fees $</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net Change in Cash and Cash Equivalents for the Period</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>0.419641</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.275001</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -14147,17 +13529,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M77" s="5" t="n">
-        <v>0.031691</v>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v>0.021947</v>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v>0.020238</v>
-      </c>
-      <c r="P77" s="5" t="n">
-        <v>0.01349</v>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -14173,22 +13563,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Net Change in Cash and Cash Equivalents for</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Cash and Cash Equivalents, Beginning of</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -14196,10 +13586,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="5" t="n">
+        <v>0.419641</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -14241,11 +13629,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O78" s="5" t="n">
-        <v>0.014476</v>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v>-0.005961</v>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -14261,31 +13653,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Net Change in Cash and Cash Equivalents for</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Cash and Cash Equivalents, End of Period $</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.419641</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.009124</v>
+        <v>0.694642</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -14317,17 +13707,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M79" s="5" t="n">
-        <v>0.128074</v>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v>0.167429</v>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v>0.16169</v>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v>0.037441</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -14343,33 +13741,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Non-cash financing and investing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Shares issued for interest in mining property $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="5" t="n">
+        <v>0.0462</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -14401,17 +13793,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="5" t="n">
-        <v>0.03766</v>
-      </c>
-      <c r="N80" s="5" t="n">
-        <v>0.027448</v>
-      </c>
-      <c r="O80" s="5" t="n">
-        <v>0.035505</v>
-      </c>
-      <c r="P80" s="5" t="n">
-        <v>0.03127</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -14437,19 +13837,23 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Filing fees $</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>0.00013</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>0.003602</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -14461,47 +13865,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="5" t="n">
+        <v>0.012455</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>0.022482</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.013583</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>0.017337</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.008439</v>
+        <v>0.031691</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.011646</v>
+        <v>0.021947</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.016312</v>
+        <v>0.020238</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.033476</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01349</v>
+      </c>
+      <c r="Q81" s="5" t="n">
+        <v>0.017434</v>
+      </c>
+      <c r="R81" s="5" t="n">
+        <v>0.01782</v>
       </c>
     </row>
     <row r="82">
@@ -14517,14 +13909,10 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation assets impairment</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -14565,27 +13953,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M82" s="5" t="n">
-        <v>0.008279</v>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v>0.008116</v>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v>0.01081</v>
-      </c>
-      <c r="P82" s="5" t="n">
-        <v>0.008458</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <v>0.08126800000000001</v>
+      </c>
+      <c r="R82" s="5" t="n">
+        <v>1.507618</v>
       </c>
     </row>
     <row r="83">
@@ -14601,19 +13993,23 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>0.006484</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.021201</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -14630,42 +14026,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J83" s="5" t="n">
+        <v>-0.01739</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.012247</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M83" s="5" t="n">
-        <v>0.009912000000000001</v>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v>0.021618</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O83" s="5" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.014476</v>
       </c>
       <c r="P83" s="5" t="n">
-        <v>0.033113</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005961</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <v>-0.021115</v>
+      </c>
+      <c r="R83" s="5" t="n">
+        <v>0.004413</v>
       </c>
     </row>
     <row r="84">
@@ -14681,77 +14073,57 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Exploration</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" s="5" t="n">
+        <v>0.009124</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.011729</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>0.032822</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0.013511</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0.017589</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0.080417</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>0.146065</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0.128074</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>0.167429</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0.16169</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.015325</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.037441</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>0.054729</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>0.041021</v>
       </c>
     </row>
     <row r="85">
@@ -14767,12 +14139,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -14780,60 +14152,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>0.007875</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.08873200000000001</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0.04067</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0.044214</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>0.038977</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0.032258</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>0.034466</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.009069000000000001</v>
+        <v>0.03766</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.009623</v>
+        <v>0.027448</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.017852</v>
+        <v>0.035505</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.016948</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03127</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <v>0.069755</v>
+      </c>
+      <c r="R85" s="5" t="n">
+        <v>0.04843</v>
       </c>
     </row>
     <row r="86">
@@ -14849,75 +14207,55 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Salaries and consulting fees</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.003602</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.006791</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>0.005469</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0.004252</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0.005271</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0.002308</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>0.00876</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.173255</v>
+        <v>0.008439</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.122469</v>
+        <v>0.011646</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.138832</v>
+        <v>0.016312</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.169061</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033476</v>
+      </c>
+      <c r="Q86" s="5" t="n">
+        <v>0.027939</v>
+      </c>
+      <c r="R86" s="5" t="n">
+        <v>0.024928</v>
       </c>
     </row>
     <row r="87">
@@ -14933,10 +14271,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Share based payments</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -14947,57 +14289,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G87" s="5" t="n">
+        <v>0.012383</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.014345</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.014683</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.007253</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0.008028</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>0.008068000000000001</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.00175</v>
+        <v>0.008279</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.217145</v>
+        <v>0.008116</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>0.20333</v>
+        <v>0.01081</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>0.272796</v>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008458</v>
+      </c>
+      <c r="Q87" s="5" t="n">
+        <v>0.009514</v>
+      </c>
+      <c r="R87" s="5" t="n">
+        <v>0.00971</v>
       </c>
     </row>
     <row r="88">
@@ -15013,67 +14339,55 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for Period $</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
-        <v>-0.050256</v>
+        <v>0.006484</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.569086</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021201</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.033044</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0.009672</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0.010154</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0.001392</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0.004373</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>0.022307</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>-0.404331</v>
+        <v>0.009912000000000001</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>-0.6128440000000001</v>
+        <v>0.021618</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>-0.627715</v>
+        <v>0.008670000000000001</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>-0.625417</v>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033113</v>
+      </c>
+      <c r="Q88" s="5" t="n">
+        <v>0.07173300000000001</v>
+      </c>
+      <c r="R88" s="5" t="n">
+        <v>0.053139</v>
       </c>
     </row>
     <row r="89">
@@ -15089,19 +14403,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Loss Per Share – Basic</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-4e-08</v>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -15133,27 +14447,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M89" s="5" t="n">
-        <v>-9e-09</v>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v>-1.2e-08</v>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P89" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.015325</v>
+      </c>
+      <c r="Q89" s="5" t="n">
+        <v>0.024043</v>
+      </c>
+      <c r="R89" s="5" t="n">
+        <v>0.004009</v>
       </c>
     </row>
     <row r="90">
@@ -15164,70 +14480,62 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>9.13242</v>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>12.486797</v>
+        <v>0.007875</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>14.793676</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016301</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0.014426</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>0.015889</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0.010503</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0.019566</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>0.014171</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>44.209332</v>
+        <v>0.009069000000000001</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>50.315441</v>
+        <v>0.009623</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>63.427431</v>
+        <v>0.017852</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>67.78396600000001</v>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016948</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="R90" s="5" t="n">
+        <v>0.015214</v>
       </c>
     </row>
     <row r="91">
@@ -15243,12 +14551,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Salaries and consulting fees</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -15281,41 +14589,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K91" s="5" t="n">
+        <v>0.14491</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>0.207136</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>-0.003798</v>
+        <v>0.173255</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0.005403</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.122469</v>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v>0.138832</v>
+      </c>
+      <c r="P91" s="5" t="n">
+        <v>0.169061</v>
+      </c>
+      <c r="Q91" s="5" t="n">
+        <v>0.243798</v>
+      </c>
+      <c r="R91" s="5" t="n">
+        <v>0.26047</v>
       </c>
     </row>
     <row r="92">
@@ -15331,7 +14627,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Exploration expenses $</t>
+          <t>Share based payments</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -15340,11 +14636,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0.049324</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>0.05928</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -15356,50 +14656,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J92" s="5" t="n">
+        <v>0.12012</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0.02888</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>0.043725</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="N92" s="5" t="n">
+        <v>0.217145</v>
+      </c>
+      <c r="O92" s="5" t="n">
+        <v>0.20333</v>
+      </c>
+      <c r="P92" s="5" t="n">
+        <v>0.272796</v>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <v>0.178683</v>
+      </c>
+      <c r="R92" s="5" t="n">
+        <v>0.093498</v>
       </c>
     </row>
     <row r="93">
@@ -15415,77 +14697,53 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Net Loss and Comprehensive Loss for Period $</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="n">
-        <v>0.009353</v>
+        <v>-0.050256</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.017474</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0.050391</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.569086</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.335652</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.178341</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-0.284432</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>-0.34657</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>-0.515338</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>-0.404331</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>-0.6128440000000001</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>-0.627715</v>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>-0.625417</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <v>-0.770821</v>
+      </c>
+      <c r="R93" s="5" t="n">
+        <v>-2.08027</v>
       </c>
     </row>
     <row r="94">
@@ -15496,84 +14754,62 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Loss Per Share – Basic</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.009124</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.011729</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-1.8e-08</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-8e-09</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-1.1e-08</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-1.4e-08</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>-9e-09</v>
+      </c>
+      <c r="N94" s="5" t="n">
+        <v>-1.2e-08</v>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="P94" s="5" t="n">
+        <v>-9e-09</v>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <v>-1.1e-08</v>
+      </c>
+      <c r="R94" s="5" t="n">
+        <v>-2.9e-08</v>
       </c>
     </row>
     <row r="95">
@@ -15584,84 +14820,56 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Weighted Average Number of Common Shares</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>9.13242</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.070893</v>
+        <v>12.486797</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.08873200000000001</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.793676</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>19.286653</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>21.611861</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>25.239489</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>33.426761</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>36.501041</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>44.209332</v>
+      </c>
+      <c r="N95" s="5" t="n">
+        <v>50.315441</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>63.427431</v>
+      </c>
+      <c r="P95" s="5" t="n">
+        <v>66.967766</v>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <v>67.382875</v>
+      </c>
+      <c r="R95" s="5" t="n">
+        <v>72.72029499999999</v>
       </c>
     </row>
     <row r="96">
@@ -15672,29 +14880,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Loss on disposition of exploration assets</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>0.003602</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0.006791</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -15741,10 +14949,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q96" s="5" t="n">
+        <v>0.08126800000000001</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -15760,17 +14966,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Rent (note 9)</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -15778,11 +14984,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F97" s="5" t="n">
-        <v>0.008711</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>0.012383</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -15804,20 +15014,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L97" s="5" t="n">
+        <v>0.013303</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>-0.003798</v>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v>0.005403</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -15848,17 +15052,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -15866,11 +15070,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>0.021201</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>0.033044</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -15887,15 +15095,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K98" s="5" t="n">
+        <v>0.012247</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>0.013303</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -15936,49 +15140,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.007875</v>
+        <v>0.027057</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.016301</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.15062</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.098693</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.063183</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0.078235</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.14491</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -16024,25 +15216,33 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Salaries</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F100" s="5" t="n">
-        <v>0.027057</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.15062</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16054,10 +15254,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J100" s="5" t="n">
+        <v>-0.01739</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -16108,12 +15306,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Exploration expenses $</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -16123,15 +15321,13 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.320908</v>
+        <v>0.049324</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.026601</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05928</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.002334</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -16192,39 +15388,33 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Consulting fees                                          44,000</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Operating Loss Before Other Items</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.009353</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.569086</v>
+        <v>0.017474</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.466955</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017474</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0.016291</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.012455</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -16280,30 +15470,34 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets                                                  -</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>(note</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>-0.234494</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.044</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.052</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -16364,34 +15558,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets                                                  -</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.569086</v>
+        <v>0.320908</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.701449</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026601</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.04893</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -16452,17 +15640,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets                                                  -</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Loss Per Share – Basic $</t>
+          <t>Operating Loss Before Other Items</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16470,16 +15658,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.466955</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>-0.335652</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -16540,29 +15728,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Impairment of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Professional fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>0.032789</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>0.070893</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>(note 6)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-0.234494</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -16628,34 +15814,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Impairment of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rent (note 8)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>0.008711</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net Loss and Comprehensive Loss for Period $</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>-0.701449</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>-0.335652</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -16716,32 +15898,34 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Impairment of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Salaries</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Loss Per Share – Basic</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="5" t="n">
-        <v>0.027057</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -16802,27 +15986,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Consulting fees                                          44,000</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.320908</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009124</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.011729</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -16888,81 +16074,1213 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.070893</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.08873200000000001</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.003602</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.006791</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Rent (note 9)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.008711</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.012383</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0.021201</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.033044</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.007875</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.016301</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.027057</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.15062</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.320908</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.026601</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Consulting fees                                          44,000</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Operating Loss Before Other Items</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>-0.569086</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>-0.466955</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets                                                  -</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>(note</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>-0.234494</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets                                                  -</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>-0.569086</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>-0.701449</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets                                                  -</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Loss Per Share – Basic $</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>Operating Expenses</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Professional fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.032789</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.070893</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Rent (note 8)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.008711</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>Operating Expenses total</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E110" s="5" t="n">
+      <c r="E123" s="5" t="n">
         <v>0.050256</v>
       </c>
-      <c r="F110" s="5" t="n">
+      <c r="F123" s="5" t="n">
         <v>0.569086</v>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
